--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Projects\GunBattleRoyale\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GunBattleRoyale\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B1573AA-8F7A-4EDF-8404-6D82DBAAB4CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{278E4B1F-5FC0-4EEB-8A57-F120D984AD4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,12 +22,21 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="126">
   <si>
     <t>载弹</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -495,22 +504,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>4（空投8发备弹）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>自带二倍镜</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>自带5-10倍镜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>60（空投120发备弹）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>格洛克</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -519,11 +516,31 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>20（复活60发备弹）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>45acp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自带4-10倍镜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HK416</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UMP45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AA12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>霰弹</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -531,6 +548,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -562,7 +582,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -570,11 +590,63 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -598,7 +670,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -606,11 +678,38 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -893,15 +992,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R27"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="8.6640625" style="3"/>
-    <col min="4" max="4" width="8.6640625" style="3" customWidth="1"/>
-    <col min="5" max="16384" width="8.6640625" style="3"/>
+    <col min="2" max="3" width="8.625" style="3"/>
+    <col min="4" max="4" width="8.625" style="3" customWidth="1"/>
+    <col min="5" max="16384" width="8.625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B1" s="3" t="s">
         <v>14</v>
       </c>
@@ -954,7 +1053,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>43</v>
       </c>
@@ -1006,7 +1105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -1058,7 +1157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>70</v>
       </c>
@@ -1095,7 +1194,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>13</v>
       </c>
@@ -1150,7 +1249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>73</v>
       </c>
@@ -1208,7 +1307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>31</v>
       </c>
@@ -1245,7 +1344,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
@@ -1303,7 +1402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
@@ -1361,7 +1460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>65</v>
       </c>
@@ -1401,7 +1500,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="O11" s="3">
         <v>6</v>
       </c>
@@ -1415,7 +1514,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>18</v>
       </c>
@@ -1429,7 +1528,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>19</v>
       </c>
@@ -1443,7 +1542,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>20</v>
       </c>
@@ -1457,7 +1556,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>21</v>
       </c>
@@ -1471,7 +1570,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>22</v>
       </c>
@@ -1494,12 +1593,12 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" s="10" t="s">
         <v>48</v>
       </c>
@@ -1536,7 +1635,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" s="10"/>
       <c r="B20" s="10"/>
       <c r="C20" s="10"/>
@@ -1574,7 +1673,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>43</v>
       </c>
@@ -1614,7 +1713,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>6</v>
       </c>
@@ -1667,7 +1766,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>13</v>
       </c>
@@ -1696,7 +1795,7 @@
         <v>0.64000000000000012</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>31</v>
       </c>
@@ -1713,7 +1812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>7</v>
       </c>
@@ -1742,7 +1841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>8</v>
       </c>
@@ -1771,7 +1870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
     </row>
@@ -1793,13 +1892,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE155047-285E-45CE-A511-9B7B3BC6DB84}">
   <dimension ref="A1:L21"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.58203125" style="1" customWidth="1"/>
-    <col min="2" max="16384" width="8.6640625" style="1"/>
+    <col min="1" max="1" width="10.625" style="1" customWidth="1"/>
+    <col min="2" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>33</v>
       </c>
@@ -1837,7 +1936,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1875,7 +1974,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1907,7 +2006,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1933,7 +2032,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1953,7 +2052,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1967,7 +2066,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1975,37 +2074,37 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>37</v>
       </c>
@@ -2016,7 +2115,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>34</v>
       </c>
@@ -2024,7 +2123,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>35</v>
       </c>
@@ -2032,7 +2131,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>36</v>
       </c>
@@ -2040,7 +2139,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>38</v>
       </c>
@@ -2048,7 +2147,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>39</v>
       </c>
@@ -2056,7 +2155,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>40</v>
       </c>
@@ -2073,13 +2172,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89779524-204D-407E-907D-88382DE78B98}">
-  <dimension ref="A1:Z18"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Z22"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="8.6640625" style="7"/>
+    <col min="1" max="16384" width="8.625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
         <v>75</v>
       </c>
@@ -2128,26 +2227,26 @@
       <c r="T1" s="11"/>
       <c r="U1" s="11"/>
       <c r="V1" s="11"/>
-      <c r="W1" s="11" t="s">
+      <c r="W1" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="X1" s="11"/>
-      <c r="Y1" s="11"/>
-      <c r="Z1" s="11"/>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="11"/>
       <c r="B2" s="11"/>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="14" t="s">
         <v>81</v>
       </c>
       <c r="G2" s="11"/>
@@ -2157,764 +2256,1068 @@
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
       <c r="M2" s="11"/>
-      <c r="N2" s="7" t="s">
+      <c r="N2" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="O2" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="P2" s="7" t="s">
+      <c r="P2" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="Q2" s="7" t="s">
+      <c r="Q2" s="14" t="s">
         <v>90</v>
       </c>
       <c r="R2" s="11"/>
-      <c r="S2" s="7" t="s">
+      <c r="S2" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="T2" s="7" t="s">
+      <c r="T2" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="U2" s="7" t="s">
+      <c r="U2" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="V2" s="7" t="s">
+      <c r="V2" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="W2" s="7" t="s">
+      <c r="W2" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="X2" s="7" t="s">
+      <c r="X2" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="Y2" s="7" t="s">
+      <c r="Y2" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="Z2" s="7" t="s">
+      <c r="Z2" s="15" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A3" s="14" t="s">
         <v>84</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="14">
         <v>21</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="14">
         <v>24</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="14">
         <v>27</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="14">
         <v>30</v>
       </c>
-      <c r="G3" s="7">
-        <v>600</v>
+      <c r="G3" s="14">
+        <v>750</v>
       </c>
       <c r="H3" s="11">
-        <v>0.25</v>
-      </c>
-      <c r="I3" s="7">
-        <v>2.5</v>
+        <v>0.3</v>
+      </c>
+      <c r="I3" s="14">
+        <v>2</v>
       </c>
       <c r="J3" s="11">
         <v>1.1499999999999999</v>
       </c>
       <c r="K3" s="11">
-        <v>100</v>
-      </c>
-      <c r="L3" s="7">
-        <v>2</v>
+        <v>120</v>
+      </c>
+      <c r="L3" s="15">
+        <f>120/G3</f>
+        <v>0.16</v>
       </c>
       <c r="M3" s="11">
         <v>2.5</v>
       </c>
-      <c r="N3" s="7">
-        <v>1</v>
-      </c>
-      <c r="O3" s="7">
-        <v>1</v>
-      </c>
-      <c r="P3" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="7">
-        <v>1</v>
-      </c>
-      <c r="R3" s="7">
+      <c r="N3" s="14">
+        <v>1</v>
+      </c>
+      <c r="O3" s="14">
+        <v>1</v>
+      </c>
+      <c r="P3" s="14">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="14">
+        <v>1</v>
+      </c>
+      <c r="R3" s="14">
         <f>G3*I3</f>
         <v>1500</v>
       </c>
-      <c r="S3" s="7">
+      <c r="S3" s="14">
         <f>C3*$I3</f>
-        <v>52.5</v>
-      </c>
-      <c r="T3" s="7">
+        <v>42</v>
+      </c>
+      <c r="T3" s="14">
         <f t="shared" ref="T3:V3" si="0">D3*$I3</f>
+        <v>48</v>
+      </c>
+      <c r="U3" s="14">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="V3" s="14">
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="U3" s="7">
-        <f t="shared" si="0"/>
-        <v>67.5</v>
-      </c>
-      <c r="V3" s="7">
-        <f t="shared" si="0"/>
-        <v>75</v>
-      </c>
-      <c r="W3" s="7">
+      <c r="W3" s="15">
         <f>C3/$G3*60</f>
-        <v>2.1</v>
-      </c>
-      <c r="X3" s="7">
+        <v>1.68</v>
+      </c>
+      <c r="X3" s="15">
         <f t="shared" ref="X3:Z3" si="1">D3/$G3*60</f>
+        <v>1.92</v>
+      </c>
+      <c r="Y3" s="15">
+        <f t="shared" si="1"/>
+        <v>2.1599999999999997</v>
+      </c>
+      <c r="Z3" s="15">
+        <f t="shared" si="1"/>
         <v>2.4</v>
       </c>
-      <c r="Y3" s="7">
-        <f t="shared" si="1"/>
-        <v>2.6999999999999997</v>
-      </c>
-      <c r="Z3" s="7">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
-        <v>107</v>
+    </row>
+    <row r="4" spans="1:26" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="B4" s="11"/>
-      <c r="C4" s="7">
-        <v>26</v>
-      </c>
-      <c r="D4" s="7">
+      <c r="C4" s="14">
+        <v>24</v>
+      </c>
+      <c r="D4" s="14">
+        <v>27</v>
+      </c>
+      <c r="E4" s="14">
         <v>30</v>
       </c>
-      <c r="E4" s="7">
-        <v>34</v>
-      </c>
-      <c r="F4" s="7">
-        <v>38</v>
-      </c>
-      <c r="G4" s="7">
-        <v>750</v>
+      <c r="F4" s="14">
+        <v>33</v>
+      </c>
+      <c r="G4" s="14">
+        <v>834</v>
       </c>
       <c r="H4" s="11"/>
-      <c r="I4" s="7">
-        <v>2</v>
+      <c r="I4" s="14">
+        <v>1.8</v>
       </c>
       <c r="J4" s="11"/>
       <c r="K4" s="11"/>
-      <c r="L4" s="7">
-        <v>1.6</v>
+      <c r="L4" s="15">
+        <f t="shared" ref="L4:L11" si="2">120/G4</f>
+        <v>0.14388489208633093</v>
       </c>
       <c r="M4" s="11"/>
-      <c r="N4" s="7">
-        <v>1</v>
-      </c>
-      <c r="O4" s="7">
-        <v>1</v>
-      </c>
-      <c r="P4" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="7">
-        <v>1</v>
-      </c>
-      <c r="R4" s="7">
-        <f t="shared" ref="R4:R11" si="2">G4*I4</f>
-        <v>1500</v>
-      </c>
-      <c r="S4" s="7">
-        <f t="shared" ref="S4:S10" si="3">C4*$I4</f>
-        <v>52</v>
-      </c>
-      <c r="T4" s="7">
-        <f t="shared" ref="T4:T10" si="4">D4*$I4</f>
-        <v>60</v>
-      </c>
-      <c r="U4" s="7">
-        <f t="shared" ref="U4:U10" si="5">E4*$I4</f>
-        <v>68</v>
-      </c>
-      <c r="V4" s="7">
-        <f t="shared" ref="V4:V10" si="6">F4*$I4</f>
-        <v>76</v>
-      </c>
-      <c r="W4" s="7">
-        <f t="shared" ref="W4:W10" si="7">C4/$G4*60</f>
-        <v>2.08</v>
-      </c>
-      <c r="X4" s="7">
-        <f t="shared" ref="X4:X10" si="8">D4/$G4*60</f>
-        <v>2.4</v>
-      </c>
-      <c r="Y4" s="7">
-        <f t="shared" ref="Y4:Y10" si="9">E4/$G4*60</f>
-        <v>2.72</v>
-      </c>
-      <c r="Z4" s="7">
-        <f t="shared" ref="Z4:Z10" si="10">F4/$G4*60</f>
-        <v>3.04</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="7">
-        <v>450</v>
+      <c r="N4" s="14">
+        <v>1</v>
+      </c>
+      <c r="O4" s="14">
+        <v>1</v>
+      </c>
+      <c r="P4" s="14">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="14">
+        <v>1</v>
+      </c>
+      <c r="R4" s="14">
+        <f>G4*I4</f>
+        <v>1501.2</v>
+      </c>
+      <c r="S4" s="14">
+        <f>C4*$I4</f>
+        <v>43.2</v>
+      </c>
+      <c r="T4" s="14">
+        <f t="shared" ref="T4" si="3">D4*$I4</f>
+        <v>48.6</v>
+      </c>
+      <c r="U4" s="14">
+        <f t="shared" ref="U4" si="4">E4*$I4</f>
+        <v>54</v>
+      </c>
+      <c r="V4" s="14">
+        <f t="shared" ref="V4" si="5">F4*$I4</f>
+        <v>59.4</v>
+      </c>
+      <c r="W4" s="15">
+        <f>C4/$G4*60</f>
+        <v>1.7266187050359714</v>
+      </c>
+      <c r="X4" s="15">
+        <f t="shared" ref="X4" si="6">D4/$G4*60</f>
+        <v>1.9424460431654675</v>
+      </c>
+      <c r="Y4" s="15">
+        <f t="shared" ref="Y4" si="7">E4/$G4*60</f>
+        <v>2.1582733812949639</v>
+      </c>
+      <c r="Z4" s="15">
+        <f t="shared" ref="Z4" si="8">F4/$G4*60</f>
+        <v>2.3741007194244603</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A5" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="B5" s="11"/>
+      <c r="C5" s="14">
+        <v>28</v>
+      </c>
+      <c r="D5" s="14">
+        <v>32</v>
+      </c>
+      <c r="E5" s="14">
+        <v>36</v>
+      </c>
+      <c r="F5" s="14">
+        <v>40</v>
+      </c>
+      <c r="G5" s="14">
+        <v>1000</v>
       </c>
       <c r="H5" s="11"/>
-      <c r="I5" s="7">
-        <v>2</v>
+      <c r="I5" s="14">
+        <v>1.5</v>
       </c>
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
-      <c r="L5" s="7">
-        <v>2.6</v>
+      <c r="L5" s="15">
+        <f t="shared" si="2"/>
+        <v>0.12</v>
       </c>
       <c r="M5" s="11"/>
-      <c r="N5" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="O5" s="11"/>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="11"/>
-      <c r="R5" s="7">
+      <c r="N5" s="14">
+        <v>1</v>
+      </c>
+      <c r="O5" s="14">
+        <v>1</v>
+      </c>
+      <c r="P5" s="14">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="14">
+        <v>1</v>
+      </c>
+      <c r="R5" s="14">
+        <f t="shared" ref="R5:R15" si="9">G5*I5</f>
+        <v>1500</v>
+      </c>
+      <c r="S5" s="14">
+        <f t="shared" ref="S5:S13" si="10">C5*$I5</f>
+        <v>42</v>
+      </c>
+      <c r="T5" s="14">
+        <f t="shared" ref="T5:T13" si="11">D5*$I5</f>
+        <v>48</v>
+      </c>
+      <c r="U5" s="14">
+        <f t="shared" ref="U5:U13" si="12">E5*$I5</f>
+        <v>54</v>
+      </c>
+      <c r="V5" s="14">
+        <f t="shared" ref="V5:V13" si="13">F5*$I5</f>
+        <v>60</v>
+      </c>
+      <c r="W5" s="15">
+        <f t="shared" ref="W5:W13" si="14">C5/$G5*60</f>
+        <v>1.68</v>
+      </c>
+      <c r="X5" s="15">
+        <f t="shared" ref="X5:X13" si="15">D5/$G5*60</f>
+        <v>1.92</v>
+      </c>
+      <c r="Y5" s="15">
+        <f t="shared" ref="Y5:Y13" si="16">E5/$G5*60</f>
+        <v>2.1599999999999997</v>
+      </c>
+      <c r="Z5" s="15">
+        <f t="shared" ref="Z5:Z13" si="17">F5/$G5*60</f>
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="C6" s="16">
+        <v>8</v>
+      </c>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="14">
+        <v>180</v>
+      </c>
+      <c r="H6" s="11"/>
+      <c r="I6" s="14">
+        <v>10</v>
+      </c>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="15">
         <f t="shared" si="2"/>
-        <v>900</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="C6" s="7">
-        <v>21</v>
-      </c>
-      <c r="D6" s="7">
-        <v>24</v>
-      </c>
-      <c r="E6" s="7">
-        <v>27</v>
-      </c>
-      <c r="F6" s="7">
-        <v>30</v>
-      </c>
-      <c r="G6" s="7">
-        <v>400</v>
-      </c>
-      <c r="H6" s="11">
-        <v>0.4</v>
-      </c>
-      <c r="I6" s="7">
-        <v>3</v>
-      </c>
-      <c r="J6" s="11">
-        <v>1.25</v>
-      </c>
-      <c r="K6" s="11">
-        <v>160</v>
-      </c>
-      <c r="L6" s="7">
-        <v>3</v>
-      </c>
-      <c r="M6" s="11">
-        <v>5</v>
-      </c>
-      <c r="N6" s="7">
-        <v>1</v>
-      </c>
-      <c r="O6" s="7">
-        <v>1</v>
-      </c>
-      <c r="P6" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="7">
-        <v>1</v>
-      </c>
-      <c r="R6" s="7">
-        <f t="shared" si="2"/>
-        <v>1200</v>
-      </c>
-      <c r="S6" s="7">
-        <f t="shared" si="3"/>
-        <v>63</v>
-      </c>
-      <c r="T6" s="7">
-        <f t="shared" si="4"/>
-        <v>72</v>
-      </c>
-      <c r="U6" s="7">
-        <f t="shared" si="5"/>
-        <v>81</v>
-      </c>
-      <c r="V6" s="7">
-        <f t="shared" si="6"/>
-        <v>90</v>
-      </c>
-      <c r="W6" s="7">
-        <f t="shared" si="7"/>
-        <v>3.15</v>
-      </c>
-      <c r="X6" s="7">
-        <f t="shared" si="8"/>
-        <v>3.5999999999999996</v>
-      </c>
-      <c r="Y6" s="7">
-        <f t="shared" si="9"/>
-        <v>4.0500000000000007</v>
-      </c>
-      <c r="Z6" s="7">
-        <f t="shared" si="10"/>
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="7">
-        <v>25</v>
-      </c>
-      <c r="D7" s="7">
-        <v>29</v>
-      </c>
-      <c r="E7" s="7">
-        <v>33</v>
-      </c>
-      <c r="F7" s="7">
-        <v>37</v>
-      </c>
-      <c r="G7" s="7">
-        <v>480</v>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="O6" s="11"/>
+      <c r="P6" s="11"/>
+      <c r="Q6" s="11"/>
+      <c r="R6" s="14">
+        <f t="shared" ref="R6" si="18">G6*I6</f>
+        <v>1800</v>
+      </c>
+      <c r="S6" s="16">
+        <f t="shared" ref="S6" si="19">C6*$I6</f>
+        <v>80</v>
+      </c>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="18"/>
+      <c r="W6" s="19">
+        <f t="shared" ref="W6" si="20">C6/$G6*60</f>
+        <v>2.666666666666667</v>
+      </c>
+      <c r="X6" s="20"/>
+      <c r="Y6" s="20"/>
+      <c r="Z6" s="21"/>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A7" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" s="11">
+        <v>20</v>
+      </c>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="14">
+        <v>450</v>
       </c>
       <c r="H7" s="11"/>
-      <c r="I7" s="7">
-        <v>2.5</v>
+      <c r="I7" s="14">
+        <v>2</v>
       </c>
       <c r="J7" s="11"/>
       <c r="K7" s="11"/>
-      <c r="L7" s="7">
-        <v>2.5</v>
+      <c r="L7" s="15">
+        <f t="shared" si="2"/>
+        <v>0.26666666666666666</v>
       </c>
       <c r="M7" s="11"/>
-      <c r="N7" s="7">
-        <v>1</v>
-      </c>
-      <c r="O7" s="7">
-        <v>1</v>
-      </c>
-      <c r="P7" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="7">
-        <v>1</v>
-      </c>
-      <c r="R7" s="7">
+      <c r="N7" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="O7" s="11"/>
+      <c r="P7" s="11"/>
+      <c r="Q7" s="11"/>
+      <c r="R7" s="14">
+        <f t="shared" si="9"/>
+        <v>900</v>
+      </c>
+      <c r="S7" s="16">
+        <f t="shared" ref="S7" si="21">C7*$I7</f>
+        <v>40</v>
+      </c>
+      <c r="T7" s="17"/>
+      <c r="U7" s="17"/>
+      <c r="V7" s="18"/>
+      <c r="W7" s="19">
+        <f t="shared" ref="W7" si="22">C7/$G7*60</f>
+        <v>2.666666666666667</v>
+      </c>
+      <c r="X7" s="20"/>
+      <c r="Y7" s="20"/>
+      <c r="Z7" s="21"/>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A8" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="C8" s="14">
+        <v>21</v>
+      </c>
+      <c r="D8" s="14">
+        <v>24</v>
+      </c>
+      <c r="E8" s="14">
+        <v>27</v>
+      </c>
+      <c r="F8" s="14">
+        <v>30</v>
+      </c>
+      <c r="G8" s="14">
+        <v>600</v>
+      </c>
+      <c r="H8" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="I8" s="14">
+        <v>2</v>
+      </c>
+      <c r="J8" s="11">
+        <v>1.25</v>
+      </c>
+      <c r="K8" s="11">
+        <v>160</v>
+      </c>
+      <c r="L8" s="15">
         <f t="shared" si="2"/>
+        <v>0.2</v>
+      </c>
+      <c r="M8" s="11">
+        <v>5</v>
+      </c>
+      <c r="N8" s="14">
+        <v>1</v>
+      </c>
+      <c r="O8" s="14">
+        <v>1</v>
+      </c>
+      <c r="P8" s="14">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="14">
+        <v>1</v>
+      </c>
+      <c r="R8" s="14">
+        <f t="shared" si="9"/>
         <v>1200</v>
       </c>
-      <c r="S7" s="7">
-        <f t="shared" si="3"/>
-        <v>62.5</v>
-      </c>
-      <c r="T7" s="7">
-        <f t="shared" si="4"/>
-        <v>72.5</v>
-      </c>
-      <c r="U7" s="7">
-        <f t="shared" si="5"/>
-        <v>82.5</v>
-      </c>
-      <c r="V7" s="7">
-        <f t="shared" si="6"/>
-        <v>92.5</v>
-      </c>
-      <c r="W7" s="7">
-        <f t="shared" si="7"/>
-        <v>3.125</v>
-      </c>
-      <c r="X7" s="7">
-        <f t="shared" si="8"/>
-        <v>3.625</v>
-      </c>
-      <c r="Y7" s="7">
-        <f t="shared" si="9"/>
-        <v>4.125</v>
-      </c>
-      <c r="Z7" s="7">
+      <c r="S8" s="14">
         <f t="shared" si="10"/>
-        <v>4.625</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="7">
-        <v>560</v>
-      </c>
-      <c r="H8" s="11"/>
-      <c r="I8" s="7">
+        <v>42</v>
+      </c>
+      <c r="T8" s="14">
+        <f t="shared" si="11"/>
+        <v>48</v>
+      </c>
+      <c r="U8" s="14">
+        <f t="shared" si="12"/>
+        <v>54</v>
+      </c>
+      <c r="V8" s="14">
+        <f t="shared" si="13"/>
+        <v>60</v>
+      </c>
+      <c r="W8" s="15">
+        <f t="shared" si="14"/>
+        <v>2.1</v>
+      </c>
+      <c r="X8" s="15">
+        <f t="shared" si="15"/>
         <v>2.4</v>
       </c>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="7">
-        <v>1.2</v>
-      </c>
-      <c r="M8" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="N8" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="7">
+      <c r="Y8" s="15">
+        <f t="shared" si="16"/>
+        <v>2.6999999999999997</v>
+      </c>
+      <c r="Z8" s="15">
+        <f t="shared" si="17"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="B9" s="11"/>
+      <c r="C9" s="14">
+        <v>24</v>
+      </c>
+      <c r="D9" s="14">
+        <v>27</v>
+      </c>
+      <c r="E9" s="14">
+        <v>30</v>
+      </c>
+      <c r="F9" s="14">
+        <v>33</v>
+      </c>
+      <c r="G9" s="14">
+        <v>667</v>
+      </c>
+      <c r="H9" s="11"/>
+      <c r="I9" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="15">
         <f t="shared" si="2"/>
-        <v>1344</v>
-      </c>
-      <c r="S8" s="11">
-        <v>144</v>
-      </c>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
-      <c r="V8" s="11"/>
-      <c r="W8" s="11">
-        <v>6</v>
-      </c>
-      <c r="X8" s="11"/>
-      <c r="Y8" s="11"/>
-      <c r="Z8" s="11"/>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="B9" s="11">
-        <v>338</v>
-      </c>
-      <c r="C9" s="7">
-        <v>4</v>
-      </c>
-      <c r="D9" s="7">
-        <v>5</v>
-      </c>
-      <c r="E9" s="7">
-        <v>6</v>
-      </c>
-      <c r="F9" s="7">
-        <v>7</v>
-      </c>
-      <c r="G9" s="7">
-        <v>50</v>
-      </c>
-      <c r="H9" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="I9" s="7">
-        <v>12</v>
-      </c>
-      <c r="J9" s="11">
+        <v>0.17991004497751126</v>
+      </c>
+      <c r="M9" s="11"/>
+      <c r="N9" s="14">
+        <v>1</v>
+      </c>
+      <c r="O9" s="14">
+        <v>1</v>
+      </c>
+      <c r="P9" s="14">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="14">
+        <v>1</v>
+      </c>
+      <c r="R9" s="14">
+        <f t="shared" ref="R9" si="23">G9*I9</f>
+        <v>1200.6000000000001</v>
+      </c>
+      <c r="S9" s="14">
+        <f t="shared" ref="S9" si="24">C9*$I9</f>
+        <v>43.2</v>
+      </c>
+      <c r="T9" s="14">
+        <f t="shared" ref="T9" si="25">D9*$I9</f>
+        <v>48.6</v>
+      </c>
+      <c r="U9" s="14">
+        <f t="shared" ref="U9" si="26">E9*$I9</f>
+        <v>54</v>
+      </c>
+      <c r="V9" s="14">
+        <f t="shared" ref="V9" si="27">F9*$I9</f>
+        <v>59.4</v>
+      </c>
+      <c r="W9" s="15">
+        <f t="shared" ref="W9" si="28">C9/$G9*60</f>
+        <v>2.1589205397301345</v>
+      </c>
+      <c r="X9" s="15">
+        <f t="shared" ref="X9" si="29">D9/$G9*60</f>
+        <v>2.4287856071964016</v>
+      </c>
+      <c r="Y9" s="15">
+        <f t="shared" ref="Y9" si="30">E9/$G9*60</f>
+        <v>2.6986506746626691</v>
+      </c>
+      <c r="Z9" s="15">
+        <f t="shared" ref="Z9" si="31">F9/$G9*60</f>
+        <v>2.9685157421289357</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A10" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="B10" s="11"/>
+      <c r="C10" s="14">
+        <v>28</v>
+      </c>
+      <c r="D10" s="14">
+        <v>32</v>
+      </c>
+      <c r="E10" s="14">
+        <v>36</v>
+      </c>
+      <c r="F10" s="14">
+        <v>40</v>
+      </c>
+      <c r="G10" s="14">
+        <v>800</v>
+      </c>
+      <c r="H10" s="11"/>
+      <c r="I10" s="14">
         <v>1.5</v>
-      </c>
-      <c r="K9" s="11">
-        <v>200</v>
-      </c>
-      <c r="M9" s="11">
-        <v>10</v>
-      </c>
-      <c r="N9" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="7">
-        <v>1</v>
-      </c>
-      <c r="R9" s="7">
-        <f t="shared" si="2"/>
-        <v>600</v>
-      </c>
-      <c r="S9" s="7">
-        <f t="shared" si="3"/>
-        <v>48</v>
-      </c>
-      <c r="T9" s="7">
-        <f t="shared" si="4"/>
-        <v>60</v>
-      </c>
-      <c r="U9" s="7">
-        <f t="shared" si="5"/>
-        <v>72</v>
-      </c>
-      <c r="V9" s="7">
-        <f t="shared" si="6"/>
-        <v>84</v>
-      </c>
-      <c r="W9" s="7">
-        <f t="shared" si="7"/>
-        <v>4.8</v>
-      </c>
-      <c r="X9" s="7">
-        <f t="shared" si="8"/>
-        <v>6</v>
-      </c>
-      <c r="Y9" s="7">
-        <f t="shared" si="9"/>
-        <v>7.1999999999999993</v>
-      </c>
-      <c r="Z9" s="7">
-        <f t="shared" si="10"/>
-        <v>8.4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="7">
-        <v>6</v>
-      </c>
-      <c r="D10" s="7">
-        <v>8</v>
-      </c>
-      <c r="E10" s="7">
-        <v>10</v>
-      </c>
-      <c r="F10" s="7">
-        <v>12</v>
-      </c>
-      <c r="G10" s="7">
-        <v>67</v>
-      </c>
-      <c r="H10" s="11"/>
-      <c r="I10" s="7">
-        <v>9</v>
       </c>
       <c r="J10" s="11"/>
       <c r="K10" s="11"/>
+      <c r="L10" s="15">
+        <f t="shared" si="2"/>
+        <v>0.15</v>
+      </c>
       <c r="M10" s="11"/>
-      <c r="N10" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="7">
-        <v>1</v>
-      </c>
-      <c r="R10" s="7">
-        <f t="shared" si="2"/>
-        <v>603</v>
-      </c>
-      <c r="S10" s="7">
-        <f t="shared" si="3"/>
+      <c r="N10" s="14">
+        <v>1</v>
+      </c>
+      <c r="O10" s="14">
+        <v>1</v>
+      </c>
+      <c r="P10" s="14">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="14">
+        <v>1</v>
+      </c>
+      <c r="R10" s="14">
+        <f t="shared" si="9"/>
+        <v>1200</v>
+      </c>
+      <c r="S10" s="14">
+        <f t="shared" si="10"/>
+        <v>42</v>
+      </c>
+      <c r="T10" s="14">
+        <f t="shared" si="11"/>
+        <v>48</v>
+      </c>
+      <c r="U10" s="14">
+        <f t="shared" si="12"/>
         <v>54</v>
       </c>
-      <c r="T10" s="7">
-        <f t="shared" si="4"/>
-        <v>72</v>
-      </c>
-      <c r="U10" s="7">
-        <f t="shared" si="5"/>
-        <v>90</v>
-      </c>
-      <c r="V10" s="7">
-        <f t="shared" si="6"/>
-        <v>108</v>
-      </c>
-      <c r="W10" s="7">
-        <f t="shared" si="7"/>
-        <v>5.3731343283582085</v>
-      </c>
-      <c r="X10" s="7">
-        <f t="shared" si="8"/>
-        <v>7.1641791044776122</v>
-      </c>
-      <c r="Y10" s="7">
-        <f t="shared" si="9"/>
-        <v>8.9552238805970141</v>
-      </c>
-      <c r="Z10" s="7">
-        <f t="shared" si="10"/>
-        <v>10.746268656716417</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>116</v>
+      <c r="V10" s="14">
+        <f t="shared" si="13"/>
+        <v>60</v>
+      </c>
+      <c r="W10" s="15">
+        <f t="shared" si="14"/>
+        <v>2.1</v>
+      </c>
+      <c r="X10" s="15">
+        <f t="shared" si="15"/>
+        <v>2.4</v>
+      </c>
+      <c r="Y10" s="15">
+        <f t="shared" si="16"/>
+        <v>2.6999999999999997</v>
+      </c>
+      <c r="Z10" s="15">
+        <f t="shared" si="17"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A11" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C11" s="11">
+        <v>60</v>
       </c>
       <c r="D11" s="11"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="7">
-        <v>30</v>
+      <c r="G11" s="14">
+        <v>750</v>
       </c>
       <c r="H11" s="11"/>
-      <c r="I11" s="7">
-        <v>20</v>
-      </c>
-      <c r="J11" s="7">
-        <v>1.75</v>
-      </c>
+      <c r="I11" s="14">
+        <v>2</v>
+      </c>
+      <c r="J11" s="11"/>
       <c r="K11" s="11"/>
-      <c r="M11" s="11"/>
+      <c r="L11" s="15">
+        <f t="shared" si="2"/>
+        <v>0.16</v>
+      </c>
+      <c r="M11" s="14">
+        <v>2.5</v>
+      </c>
       <c r="N11" s="11" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
       <c r="Q11" s="11"/>
-      <c r="R11" s="7">
-        <f t="shared" si="2"/>
+      <c r="R11" s="14">
+        <f t="shared" si="9"/>
+        <v>1500</v>
+      </c>
+      <c r="S11" s="11">
+        <f t="shared" ref="S11" si="32">C11*$I11</f>
+        <v>120</v>
+      </c>
+      <c r="T11" s="11"/>
+      <c r="U11" s="11"/>
+      <c r="V11" s="11"/>
+      <c r="W11" s="13">
+        <v>6</v>
+      </c>
+      <c r="X11" s="13"/>
+      <c r="Y11" s="13"/>
+      <c r="Z11" s="13"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A12" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="B12" s="11">
+        <v>338</v>
+      </c>
+      <c r="C12" s="14">
+        <v>4</v>
+      </c>
+      <c r="D12" s="14">
+        <v>5</v>
+      </c>
+      <c r="E12" s="14">
+        <v>6</v>
+      </c>
+      <c r="F12" s="14">
+        <v>7</v>
+      </c>
+      <c r="G12" s="14">
+        <v>50</v>
+      </c>
+      <c r="H12" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="I12" s="14">
+        <v>12</v>
+      </c>
+      <c r="J12" s="11">
+        <v>1.5</v>
+      </c>
+      <c r="K12" s="11">
+        <v>200</v>
+      </c>
+      <c r="L12" s="14"/>
+      <c r="M12" s="11">
+        <v>10</v>
+      </c>
+      <c r="N12" s="14">
+        <v>1</v>
+      </c>
+      <c r="O12" s="14"/>
+      <c r="P12" s="14"/>
+      <c r="Q12" s="14">
+        <v>1</v>
+      </c>
+      <c r="R12" s="14">
+        <f t="shared" si="9"/>
         <v>600</v>
       </c>
-      <c r="S11" s="8"/>
-      <c r="T11" s="8"/>
-      <c r="U11" s="8"/>
-      <c r="V11" s="8"/>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
+      <c r="S12" s="14">
+        <f t="shared" si="10"/>
+        <v>48</v>
+      </c>
+      <c r="T12" s="14">
+        <f t="shared" si="11"/>
+        <v>60</v>
+      </c>
+      <c r="U12" s="14">
+        <f t="shared" si="12"/>
+        <v>72</v>
+      </c>
+      <c r="V12" s="14">
+        <f t="shared" si="13"/>
+        <v>84</v>
+      </c>
+      <c r="W12" s="15">
+        <f t="shared" si="14"/>
+        <v>4.8</v>
+      </c>
+      <c r="X12" s="15">
+        <f t="shared" si="15"/>
+        <v>6</v>
+      </c>
+      <c r="Y12" s="15">
+        <f t="shared" si="16"/>
+        <v>7.1999999999999993</v>
+      </c>
+      <c r="Z12" s="15">
+        <f t="shared" si="17"/>
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A13" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="B13" s="11"/>
+      <c r="C13" s="14">
+        <v>6</v>
+      </c>
+      <c r="D13" s="14">
+        <v>8</v>
+      </c>
+      <c r="E13" s="14">
+        <v>10</v>
+      </c>
+      <c r="F13" s="14">
+        <v>12</v>
+      </c>
+      <c r="G13" s="14">
+        <v>67</v>
+      </c>
+      <c r="H13" s="11"/>
+      <c r="I13" s="14">
+        <v>9</v>
+      </c>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="14">
+        <v>1</v>
+      </c>
+      <c r="O13" s="14"/>
+      <c r="P13" s="14"/>
+      <c r="Q13" s="14">
+        <v>1</v>
+      </c>
+      <c r="R13" s="14">
+        <f t="shared" si="9"/>
+        <v>603</v>
+      </c>
+      <c r="S13" s="14">
+        <f t="shared" si="10"/>
+        <v>54</v>
+      </c>
+      <c r="T13" s="14">
+        <f t="shared" si="11"/>
+        <v>72</v>
+      </c>
+      <c r="U13" s="14">
+        <f t="shared" si="12"/>
+        <v>90</v>
+      </c>
+      <c r="V13" s="14">
+        <f t="shared" si="13"/>
+        <v>108</v>
+      </c>
+      <c r="W13" s="15">
+        <f t="shared" si="14"/>
+        <v>5.3731343283582085</v>
+      </c>
+      <c r="X13" s="15">
+        <f t="shared" si="15"/>
+        <v>7.1641791044776122</v>
+      </c>
+      <c r="Y13" s="15">
+        <f t="shared" si="16"/>
+        <v>8.9552238805970141</v>
+      </c>
+      <c r="Z13" s="15">
+        <f t="shared" si="17"/>
+        <v>10.746268656716417</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="B14" s="11"/>
+      <c r="C14" s="14">
+        <v>9</v>
+      </c>
+      <c r="D14" s="14">
+        <v>12</v>
+      </c>
+      <c r="E14" s="14">
+        <v>15</v>
+      </c>
+      <c r="F14" s="14">
+        <v>18</v>
+      </c>
+      <c r="G14" s="14">
+        <v>100</v>
+      </c>
+      <c r="H14" s="11"/>
+      <c r="I14" s="14">
+        <v>6</v>
+      </c>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="14">
+        <v>1</v>
+      </c>
+      <c r="O14" s="14"/>
+      <c r="P14" s="14"/>
+      <c r="Q14" s="14">
+        <v>1</v>
+      </c>
+      <c r="R14" s="14">
+        <f t="shared" si="9"/>
+        <v>600</v>
+      </c>
+      <c r="S14" s="14">
+        <f t="shared" ref="S14" si="33">C14*$I14</f>
+        <v>54</v>
+      </c>
+      <c r="T14" s="14">
+        <f t="shared" ref="T14" si="34">D14*$I14</f>
+        <v>72</v>
+      </c>
+      <c r="U14" s="14">
+        <f t="shared" ref="U14" si="35">E14*$I14</f>
+        <v>90</v>
+      </c>
+      <c r="V14" s="14">
+        <f t="shared" ref="V14" si="36">F14*$I14</f>
+        <v>108</v>
+      </c>
+      <c r="W14" s="15">
+        <f t="shared" ref="W14" si="37">C14/$G14*60</f>
+        <v>5.3999999999999995</v>
+      </c>
+      <c r="X14" s="15">
+        <f t="shared" ref="X14" si="38">D14/$G14*60</f>
+        <v>7.1999999999999993</v>
+      </c>
+      <c r="Y14" s="15">
+        <f t="shared" ref="Y14" si="39">E14/$G14*60</f>
+        <v>9</v>
+      </c>
+      <c r="Z14" s="15">
+        <f t="shared" ref="Z14" si="40">F14/$G14*60</f>
+        <v>10.799999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A15" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="C15" s="11">
+        <v>4</v>
+      </c>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="14">
+        <v>30</v>
+      </c>
+      <c r="H15" s="11"/>
+      <c r="I15" s="14">
+        <v>20</v>
+      </c>
+      <c r="J15" s="14">
+        <v>1.75</v>
+      </c>
+      <c r="K15" s="11"/>
+      <c r="L15" s="14"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="O15" s="11"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11"/>
+      <c r="R15" s="14">
+        <f t="shared" si="9"/>
+        <v>600</v>
+      </c>
+      <c r="S15" s="11">
+        <f t="shared" ref="S15" si="41">C15*$I15</f>
+        <v>80</v>
+      </c>
+      <c r="T15" s="11"/>
+      <c r="U15" s="11"/>
+      <c r="V15" s="11"/>
+      <c r="W15" s="13">
+        <f t="shared" ref="W15" si="42">C15/$G15*60</f>
+        <v>8</v>
+      </c>
+      <c r="X15" s="13"/>
+      <c r="Y15" s="13"/>
+      <c r="Z15" s="13"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B17" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C17" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D17" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E17" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F17" s="14" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B18" s="14">
         <v>0.5</v>
       </c>
-      <c r="C14" s="7">
-        <v>1</v>
-      </c>
-      <c r="D14" s="7">
+      <c r="C18" s="14">
+        <v>1</v>
+      </c>
+      <c r="D18" s="14">
         <v>0.2</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E18" s="14">
         <v>0.1</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F18" s="14">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A16" s="11" t="s">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="7" t="s">
+      <c r="B20" s="11"/>
+      <c r="C20" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D20" s="14" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="11" t="s">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="7">
-        <v>1</v>
-      </c>
-      <c r="D17" s="7">
+      <c r="B21" s="11"/>
+      <c r="C21" s="14">
+        <v>1</v>
+      </c>
+      <c r="D21" s="14">
         <v>0.5</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="11" t="s">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="7">
+      <c r="B22" s="11"/>
+      <c r="C22" s="14">
         <v>0.5</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D22" s="14">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="40">
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="H3:H5"/>
-    <mergeCell ref="J3:J5"/>
-    <mergeCell ref="K3:K5"/>
-    <mergeCell ref="N5:Q5"/>
-    <mergeCell ref="M3:M5"/>
-    <mergeCell ref="S8:V8"/>
-    <mergeCell ref="W8:Z8"/>
-    <mergeCell ref="N8:Q8"/>
-    <mergeCell ref="N11:Q11"/>
-    <mergeCell ref="M9:M11"/>
-    <mergeCell ref="M6:M7"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="H6:H8"/>
-    <mergeCell ref="J6:J8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="H9:H11"/>
-    <mergeCell ref="K9:K11"/>
-    <mergeCell ref="S1:V1"/>
-    <mergeCell ref="W1:Z1"/>
-    <mergeCell ref="R1:R2"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="M1:M2"/>
-    <mergeCell ref="N1:Q1"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A18:B18"/>
+  <mergeCells count="48">
+    <mergeCell ref="S7:V7"/>
+    <mergeCell ref="W7:Z7"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="N6:Q6"/>
+    <mergeCell ref="S6:V6"/>
+    <mergeCell ref="W6:Z6"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A22:B22"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="K1:K2"/>
     <mergeCell ref="A1:A2"/>
@@ -2923,10 +3326,37 @@
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="S1:V1"/>
+    <mergeCell ref="W1:Z1"/>
+    <mergeCell ref="R1:R2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:Q1"/>
+    <mergeCell ref="M8:M10"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="H8:H11"/>
+    <mergeCell ref="J8:J11"/>
+    <mergeCell ref="K8:K11"/>
+    <mergeCell ref="H12:H15"/>
+    <mergeCell ref="K12:K15"/>
+    <mergeCell ref="J12:J14"/>
+    <mergeCell ref="S11:V11"/>
+    <mergeCell ref="W11:Z11"/>
+    <mergeCell ref="N11:Q11"/>
+    <mergeCell ref="N15:Q15"/>
+    <mergeCell ref="M12:M15"/>
+    <mergeCell ref="S15:V15"/>
+    <mergeCell ref="W15:Z15"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="H3:H7"/>
+    <mergeCell ref="J3:J7"/>
+    <mergeCell ref="K3:K7"/>
+    <mergeCell ref="N7:Q7"/>
+    <mergeCell ref="M3:M7"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
